--- a/artfynd/A 22601-2024 artfynd.xlsx
+++ b/artfynd/A 22601-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>111910230</v>
       </c>
       <c r="B2" t="n">
-        <v>93045</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,7 +713,7 @@
         <v>408002</v>
       </c>
       <c r="R2" t="n">
-        <v>7039048</v>
+        <v>7039049</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,12 +779,7 @@
         <v>111910234</v>
       </c>
       <c r="B3" t="n">
-        <v>90480</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,7 +801,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111910233</v>
+        <v>111910235</v>
       </c>
       <c r="B4" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +888,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östitorpen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407943</v>
+        <v>407874</v>
       </c>
       <c r="R4" t="n">
-        <v>7039118</v>
+        <v>7039185</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,6 +975,410 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111910229</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Östitorpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>408017</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7039048</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111910236</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Östitorpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>407817</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7039312</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111910228</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Östitorpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>408036</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7039037</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111910232</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Östitorpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>408009</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7039059</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>

--- a/artfynd/A 22601-2024 artfynd.xlsx
+++ b/artfynd/A 22601-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111910230</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111910234</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111910235</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111910229</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111910236</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111910228</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,8 +1418,22 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111910232</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>